--- a/public/documents/EPO Pervisional Production.xlsx
+++ b/public/documents/EPO Pervisional Production.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Source\repos\GitHub\tools\public\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86029986-10A9-44F9-8802-84210CF355C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C577A6-AC2C-4C8E-B66E-AF4EF392B676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,8 +21,8 @@
     <sheet name="Lists" sheetId="23" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="ExamenTypes">Lists!$B$2:$B$8</definedName>
-    <definedName name="ResearchTypes">Lists!$A$2</definedName>
+    <definedName name="ExaminationTypes">Lists!$B$2:$B$8</definedName>
+    <definedName name="SearchTypes">Lists!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="121">
   <si>
     <t>January</t>
   </si>
@@ -313,12 +313,6 @@
     <t>Goals</t>
   </si>
   <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Examen</t>
-  </si>
-  <si>
     <t>1st Comm'</t>
   </si>
   <si>
@@ -386,18 +380,6 @@
     <t>Other Activities</t>
   </si>
   <si>
-    <t>Research Done</t>
-  </si>
-  <si>
-    <t>Research Objective</t>
-  </si>
-  <si>
-    <t>Examen Objective</t>
-  </si>
-  <si>
-    <t>Examen Done</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -432,12 +414,6 @@
   </si>
   <si>
     <t>1st Comm Done</t>
-  </si>
-  <si>
-    <t>Research Types</t>
-  </si>
-  <si>
-    <t>Examen Types</t>
   </si>
   <si>
     <t>1st Comm Objectives</t>
@@ -570,6 +546,27 @@
   </si>
   <si>
     <t>Example Sheet:</t>
+  </si>
+  <si>
+    <t>Search Types</t>
+  </si>
+  <si>
+    <t>Examination Types</t>
+  </si>
+  <si>
+    <t>Examination</t>
+  </si>
+  <si>
+    <t>Search Objective</t>
+  </si>
+  <si>
+    <t>Search Done</t>
+  </si>
+  <si>
+    <t>Examination Objective</t>
+  </si>
+  <si>
+    <t>Examination Done</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1572,7 +1569,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1732,6 +1728,21 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="2" fontId="8" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1845,21 +1856,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2157,7 +2153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Research</a:t>
+              <a:t>Search</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3175,7 +3171,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Examen</a:t>
+              <a:t>Examination</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -13057,22 +13053,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>563968</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>106174</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>68681</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>144291</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{026D644E-BDBB-63DE-34F7-262404EEAF5A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C457625-7380-7DCB-18A0-788D0FC1895D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13088,12 +13084,26 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="942975"/>
-          <a:ext cx="14279968" cy="10021699"/>
+          <a:off x="171450" y="1047750"/>
+          <a:ext cx="14375231" cy="10145541"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -13107,7 +13117,9 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{870F838B-71A9-4016-B63A-82CDF542D800}" name="Date" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{00C04992-4B17-4F21-8D16-F0288BC53823}" name="Action" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{D9AC4F53-8310-4E40-97CF-7AEEB53C9C97}" name="Type" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D9AC4F53-8310-4E40-97CF-7AEEB53C9C97}" name="Type" dataDxfId="14">
+      <calculatedColumnFormula>IF(B17="","",IF(B17="Search","Search","Grant"))</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="4" xr3:uid="{6101C796-DAC7-45A0-9389-4ABEB9451027}" name="File# (Optional)" dataDxfId="13"/>
     <tableColumn id="5" xr3:uid="{8DF4D7B5-A79F-4D56-8D9F-4A4B37399FFB}" name="Comment (Optional)" dataDxfId="12"/>
   </tableColumns>
@@ -13436,7 +13448,7 @@
     <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="20.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.109375" customWidth="1"/>
@@ -13453,7 +13465,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="109" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="12" t="s">
@@ -13462,81 +13474,67 @@
       <c r="C1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="110" t="s">
         <v>35</v>
       </c>
       <c r="F1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="J1" s="111" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="L1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="107" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="N1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="P1" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="105"/>
+      <c r="A2" s="109"/>
       <c r="B2" s="18">
         <v>2026</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="106"/>
+      <c r="E2" s="110"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
-      <c r="H2" s="99">
+      <c r="H2" s="98">
         <f>F2/2</f>
         <v>0</v>
       </c>
-      <c r="J2" s="108"/>
-      <c r="K2" s="16">
-        <v>0</v>
-      </c>
-      <c r="L2" s="16">
-        <v>0</v>
-      </c>
-      <c r="M2" s="16">
-        <v>0</v>
-      </c>
-      <c r="N2" s="16">
-        <v>0</v>
-      </c>
-      <c r="O2" s="16">
-        <v>0</v>
-      </c>
-      <c r="P2" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="16">
-        <v>0</v>
-      </c>
+      <c r="J2" s="112"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
@@ -13582,16 +13580,16 @@
         <v>11</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -13616,7 +13614,7 @@
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -13641,7 +13639,7 @@
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -13666,7 +13664,7 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -13692,7 +13690,7 @@
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -13718,7 +13716,7 @@
     </row>
     <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -13741,7 +13739,7 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -13790,30 +13788,30 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="102" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="103"/>
-      <c r="O14" s="103"/>
-      <c r="P14" s="103"/>
-      <c r="Q14" s="104"/>
+      <c r="G14" s="106" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="107"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="107"/>
+      <c r="P14" s="107"/>
+      <c r="Q14" s="108"/>
     </row>
     <row r="15" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
+      <c r="A15" s="113" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="114"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="115"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="79"/>
+      <c r="G15" s="78"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -13823,86 +13821,86 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="80"/>
+      <c r="Q15" s="79"/>
     </row>
     <row r="16" spans="1:20" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F16" s="4"/>
-      <c r="G16" s="79"/>
+      <c r="G16" s="78"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="80"/>
+      <c r="Q16" s="79"/>
     </row>
     <row r="17" spans="1:21" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="str">
+      <c r="A17" s="32" t="str">
         <f t="shared" ref="A17:A47" ca="1" si="1">IF(B17="","",TODAY())</f>
         <v/>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="str">
-        <f t="shared" ref="C17:C52" si="2">IF(B17="","",IF(B17="Research","Search","Grant"))</f>
+        <f>IF(B17="","",IF(B17="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="28"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="81"/>
-      <c r="I17" s="112" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="113"/>
+      <c r="G17" s="80"/>
+      <c r="I17" s="116" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="80"/>
+      <c r="Q17" s="79"/>
     </row>
     <row r="18" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="str">
+      <c r="A18" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C18:C81" si="2">IF(B18="","",IF(B18="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="28"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="81"/>
-      <c r="I18" s="100">
+      <c r="G18" s="80"/>
+      <c r="I18" s="104">
         <f>Details!G5</f>
         <v>0</v>
       </c>
-      <c r="J18" s="101"/>
+      <c r="J18" s="105"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="80"/>
+      <c r="Q18" s="79"/>
     </row>
     <row r="19" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="str">
+      <c r="A19" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -13913,17 +13911,17 @@
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="28"/>
-      <c r="G19" s="81"/>
-      <c r="I19" s="114" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="112"/>
-      <c r="Q19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="I19" s="118" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="116"/>
+      <c r="Q19" s="79"/>
       <c r="S19" s="8"/>
       <c r="T19" s="3"/>
     </row>
     <row r="20" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="str">
+      <c r="A20" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -13934,16 +13932,16 @@
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="28"/>
-      <c r="G20" s="81"/>
-      <c r="I20" s="100">
+      <c r="G20" s="80"/>
+      <c r="I20" s="104">
         <f ca="1">Details!I5</f>
         <v>0</v>
       </c>
-      <c r="J20" s="101"/>
-      <c r="Q20" s="82"/>
+      <c r="J20" s="105"/>
+      <c r="Q20" s="81"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="33" t="str">
+      <c r="A21" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -13954,11 +13952,11 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="28"/>
-      <c r="G21" s="81"/>
-      <c r="Q21" s="82"/>
+      <c r="G21" s="80"/>
+      <c r="Q21" s="81"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="str">
+      <c r="A22" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -13969,11 +13967,11 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="28"/>
-      <c r="G22" s="81"/>
-      <c r="Q22" s="82"/>
+      <c r="G22" s="80"/>
+      <c r="Q22" s="81"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A23" s="33" t="str">
+      <c r="A23" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -13984,11 +13982,11 @@
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="28"/>
-      <c r="G23" s="81"/>
-      <c r="Q23" s="82"/>
+      <c r="G23" s="80"/>
+      <c r="Q23" s="81"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24" s="33" t="str">
+      <c r="A24" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -13999,11 +13997,11 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="28"/>
-      <c r="G24" s="81"/>
-      <c r="Q24" s="82"/>
+      <c r="G24" s="80"/>
+      <c r="Q24" s="81"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" s="33" t="str">
+      <c r="A25" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14014,11 +14012,11 @@
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="28"/>
-      <c r="G25" s="81"/>
-      <c r="Q25" s="82"/>
+      <c r="G25" s="80"/>
+      <c r="Q25" s="81"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26" s="33" t="str">
+      <c r="A26" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14029,11 +14027,11 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="28"/>
-      <c r="G26" s="81"/>
-      <c r="Q26" s="82"/>
+      <c r="G26" s="80"/>
+      <c r="Q26" s="81"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="33" t="str">
+      <c r="A27" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14044,11 +14042,11 @@
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="28"/>
-      <c r="G27" s="81"/>
-      <c r="Q27" s="82"/>
+      <c r="G27" s="80"/>
+      <c r="Q27" s="81"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28" s="33" t="str">
+      <c r="A28" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14059,26 +14057,26 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="28"/>
-      <c r="G28" s="81"/>
-      <c r="Q28" s="82"/>
+      <c r="G28" s="80"/>
+      <c r="Q28" s="81"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29" s="33" t="str">
+      <c r="A29" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="B29" s="32"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="28"/>
-      <c r="G29" s="81"/>
-      <c r="Q29" s="82"/>
+      <c r="G29" s="80"/>
+      <c r="Q29" s="81"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" s="33" t="str">
+      <c r="A30" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14089,11 +14087,11 @@
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="28"/>
-      <c r="G30" s="81"/>
-      <c r="Q30" s="82"/>
+      <c r="G30" s="80"/>
+      <c r="Q30" s="81"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A31" s="33" t="str">
+      <c r="A31" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14104,12 +14102,12 @@
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="28"/>
-      <c r="G31" s="81"/>
-      <c r="Q31" s="82"/>
+      <c r="G31" s="80"/>
+      <c r="Q31" s="81"/>
       <c r="U31" s="7"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="33" t="str">
+      <c r="A32" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14120,11 +14118,11 @@
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="28"/>
-      <c r="G32" s="81"/>
-      <c r="Q32" s="82"/>
+      <c r="G32" s="80"/>
+      <c r="Q32" s="81"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="str">
+      <c r="A33" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14135,11 +14133,11 @@
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="28"/>
-      <c r="G33" s="81"/>
-      <c r="Q33" s="82"/>
+      <c r="G33" s="80"/>
+      <c r="Q33" s="81"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" s="33" t="str">
+      <c r="A34" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14150,11 +14148,11 @@
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="28"/>
-      <c r="G34" s="81"/>
-      <c r="Q34" s="82"/>
+      <c r="G34" s="80"/>
+      <c r="Q34" s="81"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" s="33" t="str">
+      <c r="A35" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14165,11 +14163,11 @@
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="28"/>
-      <c r="G35" s="81"/>
-      <c r="Q35" s="82"/>
+      <c r="G35" s="80"/>
+      <c r="Q35" s="81"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" s="33" t="str">
+      <c r="A36" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14180,11 +14178,11 @@
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="28"/>
-      <c r="G36" s="81"/>
-      <c r="Q36" s="82"/>
+      <c r="G36" s="80"/>
+      <c r="Q36" s="81"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" s="33" t="str">
+      <c r="A37" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14195,11 +14193,11 @@
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="28"/>
-      <c r="G37" s="81"/>
-      <c r="Q37" s="82"/>
+      <c r="G37" s="80"/>
+      <c r="Q37" s="81"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" s="33" t="str">
+      <c r="A38" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14210,11 +14208,11 @@
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="28"/>
-      <c r="G38" s="81"/>
-      <c r="Q38" s="82"/>
+      <c r="G38" s="80"/>
+      <c r="Q38" s="81"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" s="33" t="str">
+      <c r="A39" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14225,11 +14223,11 @@
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="28"/>
-      <c r="G39" s="81"/>
-      <c r="Q39" s="82"/>
+      <c r="G39" s="80"/>
+      <c r="Q39" s="81"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" s="33" t="str">
+      <c r="A40" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14240,11 +14238,11 @@
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="28"/>
-      <c r="G40" s="81"/>
-      <c r="Q40" s="82"/>
+      <c r="G40" s="80"/>
+      <c r="Q40" s="81"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" s="33" t="str">
+      <c r="A41" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14255,11 +14253,11 @@
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="28"/>
-      <c r="G41" s="81"/>
-      <c r="Q41" s="82"/>
+      <c r="G41" s="80"/>
+      <c r="Q41" s="81"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42" s="33" t="str">
+      <c r="A42" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14270,11 +14268,11 @@
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="28"/>
-      <c r="G42" s="81"/>
-      <c r="Q42" s="82"/>
+      <c r="G42" s="80"/>
+      <c r="Q42" s="81"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43" s="33" t="str">
+      <c r="A43" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14285,11 +14283,11 @@
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="28"/>
-      <c r="G43" s="81"/>
-      <c r="Q43" s="82"/>
+      <c r="G43" s="80"/>
+      <c r="Q43" s="81"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A44" s="33" t="str">
+      <c r="A44" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14300,11 +14298,11 @@
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="28"/>
-      <c r="G44" s="81"/>
-      <c r="Q44" s="82"/>
+      <c r="G44" s="80"/>
+      <c r="Q44" s="81"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" s="33" t="str">
+      <c r="A45" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14315,11 +14313,11 @@
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="28"/>
-      <c r="G45" s="81"/>
-      <c r="Q45" s="82"/>
+      <c r="G45" s="80"/>
+      <c r="Q45" s="81"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" s="33" t="str">
+      <c r="A46" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14330,11 +14328,11 @@
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="28"/>
-      <c r="G46" s="81"/>
-      <c r="Q46" s="82"/>
+      <c r="G46" s="80"/>
+      <c r="Q46" s="81"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A47" s="33" t="str">
+      <c r="A47" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -14345,11 +14343,11 @@
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="28"/>
-      <c r="G47" s="81"/>
-      <c r="Q47" s="82"/>
+      <c r="G47" s="80"/>
+      <c r="Q47" s="81"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" s="33" t="str">
+      <c r="A48" s="32" t="str">
         <f ca="1">IF(B48="","",TODAY())</f>
         <v/>
       </c>
@@ -14360,11 +14358,11 @@
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="28"/>
-      <c r="G48" s="81"/>
-      <c r="Q48" s="82"/>
+      <c r="G48" s="80"/>
+      <c r="Q48" s="81"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49" s="33" t="str">
+      <c r="A49" s="32" t="str">
         <f t="shared" ref="A49:A112" ca="1" si="3">IF(B49="","",TODAY())</f>
         <v/>
       </c>
@@ -14375,11 +14373,11 @@
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="28"/>
-      <c r="G49" s="81"/>
-      <c r="Q49" s="82"/>
+      <c r="G49" s="80"/>
+      <c r="Q49" s="81"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A50" s="33" t="str">
+      <c r="A50" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14390,11 +14388,11 @@
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="28"/>
-      <c r="G50" s="81"/>
-      <c r="Q50" s="82"/>
+      <c r="G50" s="80"/>
+      <c r="Q50" s="81"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A51" s="33" t="str">
+      <c r="A51" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14405,11 +14403,11 @@
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="28"/>
-      <c r="G51" s="81"/>
-      <c r="Q51" s="82"/>
+      <c r="G51" s="80"/>
+      <c r="Q51" s="81"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="str">
+      <c r="A52" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14420,430 +14418,430 @@
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="28"/>
-      <c r="G52" s="81"/>
-      <c r="Q52" s="82"/>
+      <c r="G52" s="80"/>
+      <c r="Q52" s="81"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A53" s="33" t="str">
+      <c r="A53" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="str">
-        <f t="shared" ref="C53:C96" si="4">IF(B53="","",IF(B53="Research","Search","Grant"))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="28"/>
-      <c r="G53" s="81"/>
-      <c r="Q53" s="82"/>
+      <c r="G53" s="80"/>
+      <c r="Q53" s="81"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54" s="33" t="str">
+      <c r="A54" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="28"/>
-      <c r="G54" s="81"/>
-      <c r="Q54" s="82"/>
+      <c r="G54" s="80"/>
+      <c r="Q54" s="81"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A55" s="33" t="str">
+      <c r="A55" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="28"/>
-      <c r="G55" s="81"/>
-      <c r="Q55" s="82"/>
+      <c r="G55" s="80"/>
+      <c r="Q55" s="81"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A56" s="33" t="str">
+      <c r="A56" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="28"/>
-      <c r="G56" s="81"/>
-      <c r="Q56" s="82"/>
+      <c r="G56" s="80"/>
+      <c r="Q56" s="81"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57" s="33" t="str">
+      <c r="A57" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="28"/>
-      <c r="G57" s="81"/>
-      <c r="Q57" s="82"/>
+      <c r="G57" s="80"/>
+      <c r="Q57" s="81"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A58" s="33" t="str">
+      <c r="A58" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="28"/>
-      <c r="G58" s="81"/>
-      <c r="Q58" s="82"/>
+      <c r="G58" s="80"/>
+      <c r="Q58" s="81"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A59" s="33" t="str">
+      <c r="A59" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="28"/>
-      <c r="G59" s="81"/>
-      <c r="Q59" s="82"/>
+      <c r="G59" s="80"/>
+      <c r="Q59" s="81"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A60" s="33" t="str">
+      <c r="A60" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="28"/>
-      <c r="G60" s="81"/>
-      <c r="Q60" s="82"/>
+      <c r="G60" s="80"/>
+      <c r="Q60" s="81"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61" s="33" t="str">
+      <c r="A61" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="28"/>
-      <c r="G61" s="81"/>
-      <c r="Q61" s="82"/>
+      <c r="G61" s="80"/>
+      <c r="Q61" s="81"/>
     </row>
     <row r="62" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="33" t="str">
+      <c r="A62" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="28"/>
-      <c r="G62" s="83"/>
-      <c r="H62" s="84"/>
-      <c r="I62" s="84"/>
-      <c r="J62" s="84"/>
-      <c r="K62" s="84"/>
-      <c r="L62" s="84"/>
-      <c r="M62" s="84"/>
-      <c r="N62" s="84"/>
-      <c r="O62" s="84"/>
-      <c r="P62" s="84"/>
-      <c r="Q62" s="85"/>
+      <c r="G62" s="82"/>
+      <c r="H62" s="83"/>
+      <c r="I62" s="83"/>
+      <c r="J62" s="83"/>
+      <c r="K62" s="83"/>
+      <c r="L62" s="83"/>
+      <c r="M62" s="83"/>
+      <c r="N62" s="83"/>
+      <c r="O62" s="83"/>
+      <c r="P62" s="83"/>
+      <c r="Q62" s="84"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A63" s="33" t="str">
+      <c r="A63" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="28"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A64" s="33" t="str">
+      <c r="A64" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="28"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="33" t="str">
+      <c r="A65" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="28"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="33" t="str">
+      <c r="A66" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="28"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="33" t="str">
+      <c r="A67" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="28"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="33" t="str">
+      <c r="A68" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="28"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="33" t="str">
+      <c r="A69" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="28"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="33" t="str">
+      <c r="A70" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="28"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="33" t="str">
+      <c r="A71" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="28"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="33" t="str">
+      <c r="A72" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="28"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="33" t="str">
+      <c r="A73" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="28"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="33" t="str">
+      <c r="A74" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="28"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="33" t="str">
+      <c r="A75" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="28"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="33" t="str">
+      <c r="A76" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="28"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="33" t="str">
+      <c r="A77" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="28"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="33" t="str">
+      <c r="A78" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="28"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="33" t="str">
+      <c r="A79" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="28"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="33" t="str">
+      <c r="A80" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="28"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="33" t="str">
+      <c r="A81" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="28"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="33" t="str">
+      <c r="A82" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="C82:C145" si="4">IF(B82="","",IF(B82="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="28"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="33" t="str">
+      <c r="A83" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14856,7 +14854,7 @@
       <c r="E83" s="28"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="33" t="str">
+      <c r="A84" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14869,7 +14867,7 @@
       <c r="E84" s="28"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="33" t="str">
+      <c r="A85" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14882,7 +14880,7 @@
       <c r="E85" s="28"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="33" t="str">
+      <c r="A86" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14895,7 +14893,7 @@
       <c r="E86" s="28"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="33" t="str">
+      <c r="A87" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14908,7 +14906,7 @@
       <c r="E87" s="28"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="33" t="str">
+      <c r="A88" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14921,7 +14919,7 @@
       <c r="E88" s="28"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="33" t="str">
+      <c r="A89" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14934,7 +14932,7 @@
       <c r="E89" s="28"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="33" t="str">
+      <c r="A90" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14947,7 +14945,7 @@
       <c r="E90" s="28"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="33" t="str">
+      <c r="A91" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14960,7 +14958,7 @@
       <c r="E91" s="28"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="33" t="str">
+      <c r="A92" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14973,7 +14971,7 @@
       <c r="E92" s="28"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="33" t="str">
+      <c r="A93" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14986,7 +14984,7 @@
       <c r="E93" s="28"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="33" t="str">
+      <c r="A94" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -14999,7 +14997,7 @@
       <c r="E94" s="28"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="33" t="str">
+      <c r="A95" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -15012,7 +15010,7 @@
       <c r="E95" s="28"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="33" t="str">
+      <c r="A96" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -15025,3952 +15023,3952 @@
       <c r="E96" s="28"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="33" t="str">
+      <c r="A97" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="str">
-        <f t="shared" ref="C97:C160" si="5">IF(B97="","",IF(B97="Research","Search","Grant"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="28"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="33" t="str">
+      <c r="A98" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D98" s="1"/>
       <c r="E98" s="28"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="33" t="str">
+      <c r="A99" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D99" s="1"/>
       <c r="E99" s="28"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="33" t="str">
+      <c r="A100" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D100" s="1"/>
       <c r="E100" s="28"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="33" t="str">
+      <c r="A101" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="28"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="33" t="str">
+      <c r="A102" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="28"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="33" t="str">
+      <c r="A103" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="28"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="33" t="str">
+      <c r="A104" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="28"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="33" t="str">
+      <c r="A105" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="28"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="33" t="str">
+      <c r="A106" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="28"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="33" t="str">
+      <c r="A107" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="28"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="33" t="str">
+      <c r="A108" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="28"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="33" t="str">
+      <c r="A109" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D109" s="1"/>
       <c r="E109" s="28"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="33" t="str">
+      <c r="A110" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="28"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="33" t="str">
+      <c r="A111" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="28"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="33" t="str">
+      <c r="A112" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="28"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="33" t="str">
-        <f t="shared" ref="A113:A176" ca="1" si="6">IF(B113="","",TODAY())</f>
+      <c r="A113" s="32" t="str">
+        <f t="shared" ref="A113:A176" ca="1" si="5">IF(B113="","",TODAY())</f>
         <v/>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A114" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D114" s="1"/>
       <c r="E114" s="28"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A115" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D115" s="1"/>
       <c r="E115" s="28"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A116" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="28"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A117" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="28"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A118" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="28"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A119" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="28"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A120" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="28"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A121" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="28"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A122" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="28"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A123" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="28"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A124" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="28"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A125" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="28"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A126" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="28"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A127" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="28"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A128" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="28"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A129" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="28"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A130" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="28"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A131" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="28"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A132" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A133" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="28"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A134" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="28"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A135" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="28"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A136" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="28"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A137" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B137" s="1"/>
       <c r="C137" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="28"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A138" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B138" s="1"/>
       <c r="C138" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="28"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A139" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="28"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A140" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="28"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A141" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="28"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A142" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="28"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A143" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="28"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A144" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A145" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="28"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A146" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C146:C209" si="6">IF(B146="","",IF(B146="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="28"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A147" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="28"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A148" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="28"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A149" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="28"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A150" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B150" s="1"/>
       <c r="C150" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="28"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A151" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B151" s="1"/>
       <c r="C151" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="28"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A152" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="28"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A153" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B153" s="1"/>
       <c r="C153" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="28"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A154" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="28"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A155" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B155" s="1"/>
       <c r="C155" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="28"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A156" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="28"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A157" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B157" s="1"/>
       <c r="C157" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="28"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A158" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="28"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A159" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B159" s="1"/>
       <c r="C159" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="28"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A160" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A160" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B160" s="1"/>
       <c r="C160" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="28"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A161" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B161" s="1"/>
       <c r="C161" s="1" t="str">
-        <f t="shared" ref="C161:C224" si="7">IF(B161="","",IF(B161="Research","Search","Grant"))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="28"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A162" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B162" s="1"/>
       <c r="C162" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="28"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A163" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="28"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A164" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B164" s="1"/>
       <c r="C164" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D164" s="1"/>
       <c r="E164" s="28"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A165" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B165" s="1"/>
       <c r="C165" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D165" s="1"/>
       <c r="E165" s="28"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A166" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="28"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A167" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="28"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A168" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A168" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="28"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A169" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="28"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A170" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A170" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B170" s="1"/>
       <c r="C170" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="28"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A171" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="28"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A172" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A172" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="28"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A173" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A173" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B173" s="1"/>
       <c r="C173" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="28"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A174" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A174" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B174" s="1"/>
       <c r="C174" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="28"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A175" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B175" s="1"/>
       <c r="C175" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="28"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A176" s="33" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="A176" s="32" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="B176" s="1"/>
       <c r="C176" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D176" s="1"/>
       <c r="E176" s="28"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177" s="33" t="str">
-        <f t="shared" ref="A177:A240" ca="1" si="8">IF(B177="","",TODAY())</f>
+      <c r="A177" s="32" t="str">
+        <f t="shared" ref="A177:A240" ca="1" si="7">IF(B177="","",TODAY())</f>
         <v/>
       </c>
       <c r="B177" s="1"/>
       <c r="C177" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D177" s="1"/>
       <c r="E177" s="28"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A178" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B178" s="1"/>
       <c r="C178" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D178" s="1"/>
       <c r="E178" s="28"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A179" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B179" s="1"/>
       <c r="C179" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D179" s="1"/>
       <c r="E179" s="28"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A180" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A180" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B180" s="1"/>
       <c r="C180" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D180" s="1"/>
       <c r="E180" s="28"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A181" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B181" s="1"/>
       <c r="C181" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D181" s="1"/>
       <c r="E181" s="28"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A182" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A182" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B182" s="1"/>
       <c r="C182" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D182" s="1"/>
       <c r="E182" s="28"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A183" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A183" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B183" s="1"/>
       <c r="C183" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D183" s="1"/>
       <c r="E183" s="28"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A184" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A184" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B184" s="1"/>
       <c r="C184" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D184" s="1"/>
       <c r="E184" s="28"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A185" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A185" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B185" s="1"/>
       <c r="C185" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D185" s="1"/>
       <c r="E185" s="28"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A186" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A186" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D186" s="1"/>
       <c r="E186" s="28"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A187" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A187" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B187" s="1"/>
       <c r="C187" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="28"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A188" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A188" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B188" s="1"/>
       <c r="C188" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D188" s="1"/>
       <c r="E188" s="28"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A189" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A189" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B189" s="1"/>
       <c r="C189" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D189" s="1"/>
       <c r="E189" s="28"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A190" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A190" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B190" s="1"/>
       <c r="C190" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="28"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A191" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A191" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="28"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A192" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A192" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B192" s="1"/>
       <c r="C192" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D192" s="1"/>
       <c r="E192" s="28"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A193" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A193" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B193" s="1"/>
       <c r="C193" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D193" s="1"/>
       <c r="E193" s="28"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A194" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B194" s="1"/>
       <c r="C194" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D194" s="1"/>
       <c r="E194" s="28"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A195" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A195" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B195" s="1"/>
       <c r="C195" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D195" s="1"/>
       <c r="E195" s="28"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A196" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A196" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B196" s="1"/>
       <c r="C196" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D196" s="1"/>
       <c r="E196" s="28"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A197" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A197" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B197" s="1"/>
       <c r="C197" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="28"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A198" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B198" s="1"/>
       <c r="C198" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D198" s="1"/>
       <c r="E198" s="28"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A199" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A199" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B199" s="1"/>
       <c r="C199" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D199" s="1"/>
       <c r="E199" s="28"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A200" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A200" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D200" s="1"/>
       <c r="E200" s="28"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A201" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B201" s="1"/>
       <c r="C201" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D201" s="1"/>
       <c r="E201" s="28"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A202" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B202" s="1"/>
       <c r="C202" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D202" s="1"/>
       <c r="E202" s="28"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A203" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B203" s="1"/>
       <c r="C203" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D203" s="1"/>
       <c r="E203" s="28"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A204" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="28"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A205" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A205" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B205" s="1"/>
       <c r="C205" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="28"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A206" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A206" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B206" s="1"/>
       <c r="C206" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="28"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A207" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A207" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B207" s="1"/>
       <c r="C207" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D207" s="1"/>
       <c r="E207" s="28"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A208" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A208" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B208" s="1"/>
       <c r="C208" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D208" s="1"/>
       <c r="E208" s="28"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A209" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A209" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="28"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A210" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A210" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B210" s="1"/>
       <c r="C210" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C210:C273" si="8">IF(B210="","",IF(B210="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="28"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A211" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A211" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="28"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A212" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A212" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B212" s="1"/>
       <c r="C212" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="28"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A213" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B213" s="1"/>
       <c r="C213" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D213" s="1"/>
       <c r="E213" s="28"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A214" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B214" s="1"/>
       <c r="C214" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D214" s="1"/>
       <c r="E214" s="28"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A215" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A215" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B215" s="1"/>
       <c r="C215" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D215" s="1"/>
       <c r="E215" s="28"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A216" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B216" s="1"/>
       <c r="C216" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="28"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A217" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B217" s="1"/>
       <c r="C217" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="28"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A218" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A218" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B218" s="1"/>
       <c r="C218" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="28"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A219" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A219" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B219" s="1"/>
       <c r="C219" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D219" s="1"/>
       <c r="E219" s="28"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A220" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A220" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B220" s="1"/>
       <c r="C220" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="28"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A221" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A221" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="28"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A222" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A222" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B222" s="1"/>
       <c r="C222" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="28"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A223" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A223" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B223" s="1"/>
       <c r="C223" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="28"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A224" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A224" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B224" s="1"/>
       <c r="C224" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="28"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A225" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B225" s="1"/>
       <c r="C225" s="1" t="str">
-        <f t="shared" ref="C225:C288" si="9">IF(B225="","",IF(B225="Research","Search","Grant"))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="28"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A226" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B226" s="1"/>
       <c r="C226" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="28"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A227" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B227" s="1"/>
       <c r="C227" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="28"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A228" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A228" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B228" s="1"/>
       <c r="C228" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="28"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A229" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A229" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B229" s="1"/>
       <c r="C229" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="28"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A230" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A230" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B230" s="1"/>
       <c r="C230" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="28"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A231" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A231" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D231" s="1"/>
       <c r="E231" s="28"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A232" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A232" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="28"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A233" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A233" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B233" s="1"/>
       <c r="C233" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="28"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A234" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A234" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="28"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A235" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A235" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="28"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A236" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A236" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="28"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A237" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A237" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B237" s="1"/>
       <c r="C237" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="28"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A238" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A238" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B238" s="1"/>
       <c r="C238" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D238" s="1"/>
       <c r="E238" s="28"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A239" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A239" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B239" s="1"/>
       <c r="C239" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D239" s="1"/>
       <c r="E239" s="28"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240" s="33" t="str">
-        <f t="shared" ca="1" si="8"/>
+      <c r="A240" s="32" t="str">
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="B240" s="1"/>
       <c r="C240" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D240" s="1"/>
       <c r="E240" s="28"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241" s="33" t="str">
-        <f t="shared" ref="A241:A304" ca="1" si="10">IF(B241="","",TODAY())</f>
+      <c r="A241" s="32" t="str">
+        <f t="shared" ref="A241:A304" ca="1" si="9">IF(B241="","",TODAY())</f>
         <v/>
       </c>
       <c r="B241" s="1"/>
       <c r="C241" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D241" s="1"/>
       <c r="E241" s="28"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A242" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B242" s="1"/>
       <c r="C242" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D242" s="1"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A243" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A243" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B243" s="1"/>
       <c r="C243" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D243" s="1"/>
       <c r="E243" s="28"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A244" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B244" s="1"/>
       <c r="C244" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D244" s="1"/>
       <c r="E244" s="28"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A245" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B245" s="1"/>
       <c r="C245" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D245" s="1"/>
       <c r="E245" s="28"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A246" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B246" s="1"/>
       <c r="C246" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D246" s="1"/>
       <c r="E246" s="28"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A247" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D247" s="1"/>
       <c r="E247" s="28"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A248" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D248" s="1"/>
       <c r="E248" s="28"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A249" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A249" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D249" s="1"/>
       <c r="E249" s="28"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A250" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A250" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B250" s="1"/>
       <c r="C250" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D250" s="1"/>
       <c r="E250" s="28"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A251" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A251" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B251" s="1"/>
       <c r="C251" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D251" s="1"/>
       <c r="E251" s="28"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A252" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A252" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D252" s="1"/>
       <c r="E252" s="28"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A253" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A253" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B253" s="1"/>
       <c r="C253" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D253" s="1"/>
       <c r="E253" s="28"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A254" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A254" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B254" s="1"/>
       <c r="C254" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="28"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A255" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A255" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="28"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A256" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A256" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B256" s="1"/>
       <c r="C256" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D256" s="1"/>
       <c r="E256" s="28"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A257" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A257" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B257" s="1"/>
       <c r="C257" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D257" s="1"/>
       <c r="E257" s="28"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A258" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A258" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D258" s="1"/>
       <c r="E258" s="28"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A259" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A259" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B259" s="1"/>
       <c r="C259" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D259" s="1"/>
       <c r="E259" s="28"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A260" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A260" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B260" s="1"/>
       <c r="C260" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D260" s="1"/>
       <c r="E260" s="28"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A261" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A261" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D261" s="1"/>
       <c r="E261" s="28"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A262" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A262" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B262" s="1"/>
       <c r="C262" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D262" s="1"/>
       <c r="E262" s="28"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A263" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A263" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B263" s="1"/>
       <c r="C263" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D263" s="1"/>
       <c r="E263" s="28"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A264" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A264" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D264" s="1"/>
       <c r="E264" s="28"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A265" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A265" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B265" s="1"/>
       <c r="C265" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D265" s="1"/>
       <c r="E265" s="28"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A266" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A266" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B266" s="1"/>
       <c r="C266" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D266" s="1"/>
       <c r="E266" s="28"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A267" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A267" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D267" s="1"/>
       <c r="E267" s="28"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A268" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A268" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B268" s="1"/>
       <c r="C268" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D268" s="1"/>
       <c r="E268" s="28"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A269" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A269" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B269" s="1"/>
       <c r="C269" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D269" s="1"/>
       <c r="E269" s="28"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A270" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A270" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D270" s="1"/>
       <c r="E270" s="28"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A271" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A271" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B271" s="1"/>
       <c r="C271" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D271" s="1"/>
       <c r="E271" s="28"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A272" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A272" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B272" s="1"/>
       <c r="C272" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D272" s="1"/>
       <c r="E272" s="28"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A273" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A273" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D273" s="1"/>
       <c r="E273" s="28"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A274" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A274" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B274" s="1"/>
       <c r="C274" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C274:C337" si="10">IF(B274="","",IF(B274="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D274" s="1"/>
       <c r="E274" s="28"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A275" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A275" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B275" s="1"/>
       <c r="C275" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D275" s="1"/>
       <c r="E275" s="28"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A276" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A276" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D276" s="1"/>
       <c r="E276" s="28"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A277" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A277" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B277" s="1"/>
       <c r="C277" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D277" s="1"/>
       <c r="E277" s="28"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A278" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A278" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B278" s="1"/>
       <c r="C278" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D278" s="1"/>
       <c r="E278" s="28"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A279" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A279" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D279" s="1"/>
       <c r="E279" s="28"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A280" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A280" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B280" s="1"/>
       <c r="C280" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D280" s="1"/>
       <c r="E280" s="28"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A281" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A281" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B281" s="1"/>
       <c r="C281" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D281" s="1"/>
       <c r="E281" s="28"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A282" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A282" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D282" s="1"/>
       <c r="E282" s="28"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A283" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A283" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B283" s="1"/>
       <c r="C283" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D283" s="1"/>
       <c r="E283" s="28"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A284" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A284" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B284" s="1"/>
       <c r="C284" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D284" s="1"/>
       <c r="E284" s="28"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A285" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A285" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B285" s="1"/>
       <c r="C285" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D285" s="1"/>
       <c r="E285" s="28"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A286" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A286" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B286" s="1"/>
       <c r="C286" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D286" s="1"/>
       <c r="E286" s="28"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A287" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A287" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B287" s="1"/>
       <c r="C287" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D287" s="1"/>
       <c r="E287" s="28"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A288" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A288" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B288" s="1"/>
       <c r="C288" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D288" s="1"/>
       <c r="E288" s="28"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A289" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A289" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B289" s="1"/>
       <c r="C289" s="1" t="str">
-        <f t="shared" ref="C289:C352" si="11">IF(B289="","",IF(B289="Research","Search","Grant"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D289" s="1"/>
       <c r="E289" s="28"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A290" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A290" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B290" s="1"/>
       <c r="C290" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D290" s="1"/>
       <c r="E290" s="28"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A291" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A291" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B291" s="1"/>
       <c r="C291" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D291" s="1"/>
       <c r="E291" s="28"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A292" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A292" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B292" s="1"/>
       <c r="C292" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D292" s="1"/>
       <c r="E292" s="28"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A293" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A293" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B293" s="1"/>
       <c r="C293" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D293" s="1"/>
       <c r="E293" s="28"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A294" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A294" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B294" s="1"/>
       <c r="C294" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D294" s="1"/>
       <c r="E294" s="28"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A295" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A295" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B295" s="1"/>
       <c r="C295" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D295" s="1"/>
       <c r="E295" s="28"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A296" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A296" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B296" s="1"/>
       <c r="C296" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D296" s="1"/>
       <c r="E296" s="28"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A297" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A297" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B297" s="1"/>
       <c r="C297" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D297" s="1"/>
       <c r="E297" s="28"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A298" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A298" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B298" s="1"/>
       <c r="C298" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D298" s="1"/>
       <c r="E298" s="28"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A299" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A299" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D299" s="1"/>
       <c r="E299" s="28"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A300" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A300" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B300" s="1"/>
       <c r="C300" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D300" s="1"/>
       <c r="E300" s="28"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A301" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A301" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B301" s="1"/>
       <c r="C301" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D301" s="1"/>
       <c r="E301" s="28"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A302" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A302" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B302" s="1"/>
       <c r="C302" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D302" s="1"/>
       <c r="E302" s="28"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A303" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A303" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B303" s="1"/>
       <c r="C303" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D303" s="1"/>
       <c r="E303" s="28"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A304" s="33" t="str">
-        <f t="shared" ca="1" si="10"/>
+      <c r="A304" s="32" t="str">
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="B304" s="1"/>
       <c r="C304" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D304" s="1"/>
       <c r="E304" s="28"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A305" s="33" t="str">
-        <f t="shared" ref="A305:A368" ca="1" si="12">IF(B305="","",TODAY())</f>
+      <c r="A305" s="32" t="str">
+        <f t="shared" ref="A305:A368" ca="1" si="11">IF(B305="","",TODAY())</f>
         <v/>
       </c>
       <c r="B305" s="1"/>
       <c r="C305" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D305" s="1"/>
       <c r="E305" s="28"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A306" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A306" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B306" s="1"/>
       <c r="C306" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D306" s="1"/>
       <c r="E306" s="28"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A307" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A307" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B307" s="1"/>
       <c r="C307" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D307" s="1"/>
       <c r="E307" s="28"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A308" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A308" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B308" s="1"/>
       <c r="C308" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D308" s="1"/>
       <c r="E308" s="28"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A309" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A309" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B309" s="1"/>
       <c r="C309" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D309" s="1"/>
       <c r="E309" s="28"/>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A310" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A310" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B310" s="1"/>
       <c r="C310" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D310" s="1"/>
       <c r="E310" s="28"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A311" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A311" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B311" s="1"/>
       <c r="C311" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D311" s="1"/>
       <c r="E311" s="28"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A312" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A312" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B312" s="1"/>
       <c r="C312" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D312" s="1"/>
       <c r="E312" s="28"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A313" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A313" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B313" s="1"/>
       <c r="C313" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D313" s="1"/>
       <c r="E313" s="28"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A314" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A314" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B314" s="1"/>
       <c r="C314" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D314" s="1"/>
       <c r="E314" s="28"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A315" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A315" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B315" s="1"/>
       <c r="C315" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D315" s="1"/>
       <c r="E315" s="28"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A316" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A316" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B316" s="1"/>
       <c r="C316" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D316" s="1"/>
       <c r="E316" s="28"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A317" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A317" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B317" s="1"/>
       <c r="C317" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D317" s="1"/>
       <c r="E317" s="28"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A318" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A318" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B318" s="1"/>
       <c r="C318" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D318" s="1"/>
       <c r="E318" s="28"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A319" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A319" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B319" s="1"/>
       <c r="C319" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D319" s="1"/>
       <c r="E319" s="28"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A320" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A320" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B320" s="1"/>
       <c r="C320" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D320" s="1"/>
       <c r="E320" s="28"/>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A321" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A321" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B321" s="1"/>
       <c r="C321" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D321" s="1"/>
       <c r="E321" s="28"/>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A322" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A322" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B322" s="1"/>
       <c r="C322" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D322" s="1"/>
       <c r="E322" s="28"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A323" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A323" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B323" s="1"/>
       <c r="C323" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D323" s="1"/>
       <c r="E323" s="28"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A324" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A324" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B324" s="1"/>
       <c r="C324" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D324" s="1"/>
       <c r="E324" s="28"/>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A325" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A325" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B325" s="1"/>
       <c r="C325" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D325" s="1"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A326" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A326" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D326" s="1"/>
       <c r="E326" s="28"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A327" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A327" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B327" s="1"/>
       <c r="C327" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D327" s="1"/>
       <c r="E327" s="28"/>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A328" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A328" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B328" s="1"/>
       <c r="C328" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D328" s="1"/>
       <c r="E328" s="28"/>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A329" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A329" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B329" s="1"/>
       <c r="C329" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D329" s="1"/>
       <c r="E329" s="28"/>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A330" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A330" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B330" s="1"/>
       <c r="C330" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D330" s="1"/>
       <c r="E330" s="28"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A331" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A331" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B331" s="1"/>
       <c r="C331" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D331" s="1"/>
       <c r="E331" s="28"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A332" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A332" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B332" s="1"/>
       <c r="C332" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D332" s="1"/>
       <c r="E332" s="28"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A333" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A333" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B333" s="1"/>
       <c r="C333" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D333" s="1"/>
       <c r="E333" s="28"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A334" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A334" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B334" s="1"/>
       <c r="C334" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D334" s="1"/>
       <c r="E334" s="28"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A335" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A335" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B335" s="1"/>
       <c r="C335" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D335" s="1"/>
       <c r="E335" s="28"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A336" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A336" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B336" s="1"/>
       <c r="C336" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D336" s="1"/>
       <c r="E336" s="28"/>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A337" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A337" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B337" s="1"/>
       <c r="C337" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D337" s="1"/>
       <c r="E337" s="28"/>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A338" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A338" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B338" s="1"/>
       <c r="C338" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C338:C400" si="12">IF(B338="","",IF(B338="Search","Search","Grant"))</f>
         <v/>
       </c>
       <c r="D338" s="1"/>
       <c r="E338" s="28"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A339" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A339" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B339" s="1"/>
       <c r="C339" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D339" s="1"/>
       <c r="E339" s="28"/>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A340" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A340" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B340" s="1"/>
       <c r="C340" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D340" s="1"/>
       <c r="E340" s="28"/>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A341" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A341" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B341" s="1"/>
       <c r="C341" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D341" s="1"/>
       <c r="E341" s="28"/>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A342" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A342" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B342" s="1"/>
       <c r="C342" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D342" s="1"/>
       <c r="E342" s="28"/>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A343" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A343" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B343" s="1"/>
       <c r="C343" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D343" s="1"/>
       <c r="E343" s="28"/>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A344" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A344" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B344" s="1"/>
       <c r="C344" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D344" s="1"/>
       <c r="E344" s="28"/>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A345" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A345" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B345" s="1"/>
       <c r="C345" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D345" s="1"/>
       <c r="E345" s="28"/>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A346" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A346" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B346" s="1"/>
       <c r="C346" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D346" s="1"/>
       <c r="E346" s="28"/>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A347" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A347" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B347" s="1"/>
       <c r="C347" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D347" s="1"/>
       <c r="E347" s="28"/>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A348" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A348" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B348" s="1"/>
       <c r="C348" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D348" s="1"/>
       <c r="E348" s="28"/>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A349" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A349" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B349" s="1"/>
       <c r="C349" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D349" s="1"/>
       <c r="E349" s="28"/>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A350" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A350" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B350" s="1"/>
       <c r="C350" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D350" s="1"/>
       <c r="E350" s="28"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A351" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A351" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D351" s="1"/>
       <c r="E351" s="28"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A352" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A352" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B352" s="1"/>
       <c r="C352" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D352" s="1"/>
       <c r="E352" s="28"/>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A353" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A353" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="str">
-        <f t="shared" ref="C353:C400" si="13">IF(B353="","",IF(B353="Research","Search","Grant"))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D353" s="1"/>
       <c r="E353" s="28"/>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A354" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A354" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B354" s="1"/>
       <c r="C354" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D354" s="1"/>
       <c r="E354" s="28"/>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A355" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A355" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B355" s="1"/>
       <c r="C355" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D355" s="1"/>
       <c r="E355" s="28"/>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A356" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A356" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B356" s="1"/>
       <c r="C356" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D356" s="1"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A357" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A357" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B357" s="1"/>
       <c r="C357" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D357" s="1"/>
       <c r="E357" s="28"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A358" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A358" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B358" s="1"/>
       <c r="C358" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D358" s="1"/>
       <c r="E358" s="28"/>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A359" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A359" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B359" s="1"/>
       <c r="C359" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D359" s="1"/>
       <c r="E359" s="28"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A360" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A360" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B360" s="1"/>
       <c r="C360" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D360" s="1"/>
       <c r="E360" s="28"/>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A361" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A361" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B361" s="1"/>
       <c r="C361" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D361" s="1"/>
       <c r="E361" s="28"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A362" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A362" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B362" s="1"/>
       <c r="C362" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D362" s="1"/>
       <c r="E362" s="28"/>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A363" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A363" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B363" s="1"/>
       <c r="C363" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D363" s="1"/>
       <c r="E363" s="28"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A364" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A364" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B364" s="1"/>
       <c r="C364" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D364" s="1"/>
       <c r="E364" s="28"/>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A365" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A365" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B365" s="1"/>
       <c r="C365" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D365" s="1"/>
       <c r="E365" s="28"/>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A366" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A366" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B366" s="1"/>
       <c r="C366" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D366" s="1"/>
       <c r="E366" s="28"/>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A367" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A367" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D367" s="1"/>
       <c r="E367" s="28"/>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A368" s="33" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A368" s="32" t="str">
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="B368" s="1"/>
       <c r="C368" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D368" s="1"/>
       <c r="E368" s="28"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A369" s="33" t="str">
-        <f t="shared" ref="A369:A400" ca="1" si="14">IF(B369="","",TODAY())</f>
+      <c r="A369" s="32" t="str">
+        <f t="shared" ref="A369:A400" ca="1" si="13">IF(B369="","",TODAY())</f>
         <v/>
       </c>
       <c r="B369" s="1"/>
       <c r="C369" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="28"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A370" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A370" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B370" s="1"/>
       <c r="C370" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="28"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A371" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A371" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B371" s="1"/>
       <c r="C371" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D371" s="1"/>
       <c r="E371" s="28"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A372" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A372" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D372" s="1"/>
       <c r="E372" s="28"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A373" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A373" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B373" s="1"/>
       <c r="C373" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D373" s="1"/>
       <c r="E373" s="28"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A374" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A374" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B374" s="1"/>
       <c r="C374" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D374" s="1"/>
       <c r="E374" s="28"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A375" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A375" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B375" s="1"/>
       <c r="C375" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D375" s="1"/>
       <c r="E375" s="28"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A376" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A376" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B376" s="1"/>
       <c r="C376" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D376" s="1"/>
       <c r="E376" s="28"/>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A377" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A377" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B377" s="1"/>
       <c r="C377" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D377" s="1"/>
       <c r="E377" s="28"/>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A378" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A378" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B378" s="1"/>
       <c r="C378" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D378" s="1"/>
       <c r="E378" s="28"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A379" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A379" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B379" s="1"/>
       <c r="C379" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D379" s="1"/>
       <c r="E379" s="28"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A380" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A380" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B380" s="1"/>
       <c r="C380" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D380" s="1"/>
       <c r="E380" s="28"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A381" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A381" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B381" s="1"/>
       <c r="C381" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D381" s="1"/>
       <c r="E381" s="28"/>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A382" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A382" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B382" s="1"/>
       <c r="C382" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D382" s="1"/>
       <c r="E382" s="28"/>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A383" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A383" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B383" s="1"/>
       <c r="C383" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D383" s="1"/>
       <c r="E383" s="28"/>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A384" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A384" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B384" s="1"/>
       <c r="C384" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D384" s="1"/>
       <c r="E384" s="28"/>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A385" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A385" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B385" s="1"/>
       <c r="C385" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D385" s="1"/>
       <c r="E385" s="28"/>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A386" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A386" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B386" s="1"/>
       <c r="C386" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D386" s="1"/>
       <c r="E386" s="28"/>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A387" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A387" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B387" s="1"/>
       <c r="C387" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D387" s="1"/>
       <c r="E387" s="28"/>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A388" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A388" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B388" s="1"/>
       <c r="C388" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D388" s="1"/>
       <c r="E388" s="28"/>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A389" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A389" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B389" s="1"/>
       <c r="C389" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D389" s="1"/>
       <c r="E389" s="28"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A390" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A390" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B390" s="1"/>
       <c r="C390" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D390" s="1"/>
       <c r="E390" s="28"/>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A391" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A391" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B391" s="1"/>
       <c r="C391" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D391" s="1"/>
       <c r="E391" s="28"/>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A392" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A392" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B392" s="1"/>
       <c r="C392" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D392" s="1"/>
       <c r="E392" s="28"/>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A393" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A393" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B393" s="1"/>
       <c r="C393" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D393" s="1"/>
       <c r="E393" s="28"/>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A394" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A394" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B394" s="1"/>
       <c r="C394" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D394" s="1"/>
       <c r="E394" s="28"/>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A395" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A395" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B395" s="1"/>
       <c r="C395" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D395" s="1"/>
       <c r="E395" s="28"/>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A396" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A396" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B396" s="1"/>
       <c r="C396" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D396" s="1"/>
       <c r="E396" s="28"/>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A397" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A397" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B397" s="1"/>
       <c r="C397" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D397" s="1"/>
       <c r="E397" s="28"/>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A398" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A398" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B398" s="1"/>
       <c r="C398" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D398" s="1"/>
       <c r="E398" s="28"/>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A399" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A399" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B399" s="1"/>
       <c r="C399" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D399" s="1"/>
       <c r="E399" s="28"/>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A400" s="33" t="str">
-        <f t="shared" ca="1" si="14"/>
+      <c r="A400" s="32" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="B400" s="1"/>
       <c r="C400" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D400" s="1"/>
@@ -18996,7 +18994,7 @@
       <formula>ROUND(I20,2)&lt;=ROUND(I18,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{1C9BB48C-4BE7-46D2-8919-4C2354BDFFE4}">
       <formula1>"2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030"</formula1>
     </dataValidation>
@@ -19006,11 +19004,17 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Type" error="Please select a valid type from the dropdown." sqref="C754:C771" xr:uid="{5E36AE23-A027-4D96-BDD8-367A80BFC827}">
       <formula1>"Search,Grant,Dead,Refusal,IPER,1st Communication,Intermediate Communication,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Action" error="Please select 'Research' or 'Examen'." sqref="B17:B771" xr:uid="{D2BD9A3C-BA87-444E-A1F9-7651CDBBA67F}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Action" error="Please select 'Research' or 'Examen'." sqref="B401:B771" xr:uid="{D2BD9A3C-BA87-444E-A1F9-7651CDBBA67F}">
       <formula1>"Research,Examen"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Type" error="Please select a valid type. Research actions can only have 'Search'. Examen actions have multiple options." sqref="C17:C753" xr:uid="{A673F984-9E0D-4714-B0F9-94D5F279DE4D}">
-      <formula1>INDIRECT(IF(B17="Research","ResearchTypes","ExamenTypes"))</formula1>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Type" error="Please select a valid type. Research actions can only have 'Search'. Examen actions have multiple options." sqref="C401:C753" xr:uid="{A673F984-9E0D-4714-B0F9-94D5F279DE4D}">
+      <formula1>INDIRECT(IF(B401="Research","ResearchTypes","ExamenTypes"))</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Action" error="Please select 'Research' or 'Examen'." sqref="B17:B400" xr:uid="{371625E2-5260-4701-89E1-38E11D7A24A5}">
+      <formula1>"Search,Examination"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Type" error="Please select a valid type. Research actions can only have 'Search'. Examen actions have multiple options." sqref="C17:C400" xr:uid="{07F93B15-EA5D-4C3C-87F9-CD5CF845D61B}">
+      <formula1>INDIRECT(IF(B17="Search","SearchTypes","ExaminationTypes"))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19053,222 +19057,222 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="120" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
+      <c r="A1" s="124" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
       <c r="Q1"/>
       <c r="R1"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="130" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
+      <c r="A2" s="134" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="134"/>
+      <c r="N2" s="134"/>
+      <c r="O2" s="134"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="131" t="s">
+      <c r="A4" s="135" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="E4" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G4" s="133" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="134"/>
-      <c r="I4" s="135" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="137" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="138"/>
+      <c r="I4" s="139" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="137"/>
+      <c r="L4" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="133"/>
-      <c r="L4" s="136" t="s">
-        <v>56</v>
-      </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="136" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" s="137"/>
+      <c r="M4" s="141"/>
+      <c r="N4" s="140" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="141"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="132"/>
-      <c r="B5" s="50">
+      <c r="A5" s="136"/>
+      <c r="B5" s="49">
         <f>'Work Sheet'!F2</f>
         <v>0</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="49">
         <f>'Work Sheet'!G2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="49">
         <f>'Work Sheet'!H2</f>
         <v>0</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="49">
         <f>B5+C5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="100">
+      <c r="G5" s="104">
         <f>IFERROR((N9-L5)/SUM('Work Sheet'!F2:G2),0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="101"/>
-      <c r="I5" s="100" cm="1">
+      <c r="H5" s="105"/>
+      <c r="I5" s="104" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">IF(INDEX(B20:M20,MONTH(TODAY()))=0,0,(SUMPRODUCT((COLUMN(B11:M11)-COLUMN(B11)&lt;MONTH(TODAY())-1)*B11:M11)+INDEX(B11:M11,1,MONTH(TODAY()))*DAY(TODAY())/DAY(EOMONTH(TODAY(),0)))/INDEX(B20:M20,MONTH(TODAY())))</f>
         <v>0</v>
       </c>
-      <c r="J5" s="101"/>
-      <c r="L5" s="121">
+      <c r="J5" s="105"/>
+      <c r="L5" s="125">
         <f>SUM('Work Sheet'!L2:O2)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="123"/>
-      <c r="N5" s="121">
+      <c r="M5" s="127"/>
+      <c r="N5" s="125">
         <f>N9-L5</f>
         <v>253</v>
       </c>
-      <c r="O5" s="122"/>
+      <c r="O5" s="126"/>
     </row>
     <row r="7" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="N8" s="36" t="s">
-        <v>50</v>
+      <c r="N8" s="35" t="s">
+        <v>48</v>
       </c>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="43" cm="1">
+      <c r="A9" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="42" cm="1">
         <f t="array" ref="B9">NETWORKDAYS(DATE('Work Sheet'!$B$2,1,1),EOMONTH(DATE('Work Sheet'!$B$2,1,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=1)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>20</v>
       </c>
-      <c r="C9" s="43" cm="1">
+      <c r="C9" s="42" cm="1">
         <f t="array" ref="C9">NETWORKDAYS(DATE('Work Sheet'!$B$2,2,1),EOMONTH(DATE('Work Sheet'!$B$2,2,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=2)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>20</v>
       </c>
-      <c r="D9" s="43" cm="1">
+      <c r="D9" s="42" cm="1">
         <f t="array" ref="D9">NETWORKDAYS(DATE('Work Sheet'!$B$2,3,1),EOMONTH(DATE('Work Sheet'!$B$2,3,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=3)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>22</v>
       </c>
-      <c r="E9" s="43" cm="1">
+      <c r="E9" s="42" cm="1">
         <f t="array" ref="E9">NETWORKDAYS(DATE('Work Sheet'!$B$2,4,1),EOMONTH(DATE('Work Sheet'!$B$2,4,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=4)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>20</v>
       </c>
-      <c r="F9" s="43" cm="1">
+      <c r="F9" s="42" cm="1">
         <f t="array" ref="F9">NETWORKDAYS(DATE('Work Sheet'!$B$2,5,1),EOMONTH(DATE('Work Sheet'!$B$2,5,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=5)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>18</v>
       </c>
-      <c r="G9" s="43" cm="1">
+      <c r="G9" s="42" cm="1">
         <f t="array" ref="G9">NETWORKDAYS(DATE('Work Sheet'!$B$2,6,1),EOMONTH(DATE('Work Sheet'!$B$2,6,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=6)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>22</v>
       </c>
-      <c r="H9" s="43" cm="1">
+      <c r="H9" s="42" cm="1">
         <f t="array" ref="H9">NETWORKDAYS(DATE('Work Sheet'!$B$2,7,1),EOMONTH(DATE('Work Sheet'!$B$2,7,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=7)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>23</v>
       </c>
-      <c r="I9" s="43" cm="1">
+      <c r="I9" s="42" cm="1">
         <f t="array" ref="I9">NETWORKDAYS(DATE('Work Sheet'!$B$2,8,1),EOMONTH(DATE('Work Sheet'!$B$2,8,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=8)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>21</v>
       </c>
-      <c r="J9" s="43" cm="1">
+      <c r="J9" s="42" cm="1">
         <f t="array" ref="J9">NETWORKDAYS(DATE('Work Sheet'!$B$2,9,1),EOMONTH(DATE('Work Sheet'!$B$2,9,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=9)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>22</v>
       </c>
-      <c r="K9" s="43" cm="1">
+      <c r="K9" s="42" cm="1">
         <f t="array" ref="K9">NETWORKDAYS(DATE('Work Sheet'!$B$2,10,1),EOMONTH(DATE('Work Sheet'!$B$2,10,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=10)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>22</v>
       </c>
-      <c r="L9" s="43" cm="1">
+      <c r="L9" s="42" cm="1">
         <f t="array" ref="L9">NETWORKDAYS(DATE('Work Sheet'!$B$2,11,1),EOMONTH(DATE('Work Sheet'!$B$2,11,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=11)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>21</v>
       </c>
-      <c r="M9" s="43" cm="1">
+      <c r="M9" s="42" cm="1">
         <f t="array" ref="M9">NETWORKDAYS(DATE('Work Sheet'!$B$2,12,1),EOMONTH(DATE('Work Sheet'!$B$2,12,1),0))-SUMPRODUCT((Holidays!$A$2:$A$331='Work Sheet'!$C$2)*(YEAR(Holidays!$B$2:$B$331)='Work Sheet'!$B$2)*(MONTH(Holidays!$B$2:$B$331)=12)*(WEEKDAY(Holidays!$B$2:$B$331,2)&lt;=5))</f>
         <v>22</v>
       </c>
-      <c r="N9" s="44">
+      <c r="N9" s="43">
         <f>SUM(B9:M9)</f>
         <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>55</v>
+      <c r="A10" s="36" t="s">
+        <v>53</v>
       </c>
       <c r="B10" s="19">
         <f>SUM('Work Sheet'!B6:B10)</f>
@@ -19318,862 +19322,862 @@
         <f>SUM('Work Sheet'!M6:M10)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="38">
+      <c r="N10" s="37">
         <f>SUM(B10:M10)</f>
         <v>0</v>
       </c>
       <c r="T10" s="7"/>
     </row>
     <row r="11" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="45">
+      <c r="A11" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="44">
         <f t="shared" ref="B11:M11" si="0">B9-SUM(B10:B10)</f>
         <v>20</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="44">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="44">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="44">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="44">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="44">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="K11" s="45">
+      <c r="K11" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="L11" s="45">
+      <c r="L11" s="44">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="M11" s="45">
+      <c r="M11" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="N11" s="46">
+      <c r="N11" s="45">
         <f>SUM(B11:M11)</f>
         <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="127" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="128"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="129"/>
-      <c r="O12" s="55" t="s">
+      <c r="A12" s="131" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="46">
+        <f>B11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="46">
+        <f>C11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="46">
+        <f>D11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="46">
+        <f>E11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="46">
+        <f>F11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="46">
+        <f>G11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="46">
+        <f>H11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="46">
+        <f>I11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="46">
+        <f>J11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="46">
+        <f>K11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="46">
+        <f>L11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="46">
+        <f>M11*('Work Sheet'!$F$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="52">
+        <f>SUM(B13:M13)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1))</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1))</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1))</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1))</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1))</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1))</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Search",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="53">
+        <f>SUM(B14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="56">
+        <f>IFERROR(N14/B5,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="46">
+        <f>B11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="46">
+        <f>C11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="46">
+        <f>D11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="46">
+        <f>E11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="46">
+        <f>F11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="46">
+        <f>G11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="46">
+        <f>H11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="46">
+        <f>I11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="46">
+        <f>J11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="46">
+        <f>K11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="46">
+        <f>L11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="46">
+        <f>M11*('Work Sheet'!$G$2/$N$5)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="52">
+        <f>SUM(B15:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="55"/>
+    </row>
+    <row r="16" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="48">
+        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examination",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="53">
+        <f>SUM(B16:M16)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="56">
+        <f>IFERROR(N16/C5,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="65" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="47">
-        <f>B11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="47">
-        <f>C11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="47">
-        <f>D11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="47">
-        <f>E11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="47">
-        <f>F11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="47">
-        <f>G11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="47">
-        <f>H11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="47">
-        <f>I11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="47">
-        <f>J11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="47">
-        <f>K11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="47">
-        <f>L11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="47">
-        <f>M11*('Work Sheet'!$F$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="53">
-        <f>SUM(B13:M13)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="56"/>
-    </row>
-    <row r="14" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1))</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1))</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1))</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1))</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1))</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1))</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1))</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1))</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1))</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1))</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1))</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Research",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1))</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="54">
-        <f>SUM(B14:M14)</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="57">
-        <f>IFERROR(N14/B5,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="47">
-        <f>B11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="47">
-        <f>C11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="47">
-        <f>D11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="47">
-        <f>E11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="47">
-        <f>F11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="47">
-        <f>G11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="47">
-        <f>H11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="47">
-        <f>I11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="47">
-        <f>J11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="47">
-        <f>K11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="47">
-        <f>L11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="47">
-        <f>M11*('Work Sheet'!$G$2/$N$5)</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="53">
-        <f>SUM(B15:M15)</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="56"/>
-    </row>
-    <row r="16" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="49">
-        <f>COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"Grant")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"Dead")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"Refusal")+COUNTIFS('Work Sheet'!$B$17:$B$400,"Examen",'Work Sheet'!$A$17:$A$400,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$400,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1),'Work Sheet'!$C$17:$C$400,"IPER")</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="54">
-        <f>SUM(B16:M16)</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="57">
-        <f>IFERROR(N16/C5,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="67">
+      <c r="B17" s="66">
         <f>B13+B15</f>
         <v>0</v>
       </c>
-      <c r="C17" s="67">
+      <c r="C17" s="66">
         <f t="shared" ref="C17:N17" si="1">C13+C15</f>
         <v>0</v>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E17" s="67">
+      <c r="E17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="67">
+      <c r="G17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H17" s="67">
+      <c r="H17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="67">
+      <c r="I17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="67">
+      <c r="J17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="67">
+      <c r="K17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="67">
+      <c r="L17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M17" s="67">
+      <c r="M17" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="68">
+      <c r="N17" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="72">
+      <c r="A18" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="71">
         <f>B14+B16</f>
         <v>0</v>
       </c>
-      <c r="C18" s="72">
+      <c r="C18" s="71">
         <f t="shared" ref="C18:N18" si="2">C14+C16</f>
         <v>0</v>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E18" s="72">
+      <c r="E18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G18" s="72">
+      <c r="G18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H18" s="72">
+      <c r="H18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="72">
+      <c r="I18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="72">
+      <c r="J18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K18" s="72">
+      <c r="K18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="72">
+      <c r="L18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M18" s="72">
+      <c r="M18" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N18" s="70">
+      <c r="N18" s="69">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O18" s="52"/>
+      <c r="O18" s="51"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="65">
+      <c r="A19" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="64">
         <f>SUM($B$17:B17)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="65">
+      <c r="C19" s="64">
         <f>SUM($B$17:C17)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="65">
+      <c r="D19" s="64">
         <f>SUM($B$17:D17)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="65">
+      <c r="E19" s="64">
         <f>SUM($B$17:E17)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="65">
+      <c r="F19" s="64">
         <f>SUM($B$17:F17)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="65">
+      <c r="G19" s="64">
         <f>SUM($B$17:G17)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="65">
+      <c r="H19" s="64">
         <f>SUM($B$17:H17)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="64">
         <f>SUM($B$17:I17)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="65">
+      <c r="J19" s="64">
         <f>SUM($B$17:J17)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="65">
+      <c r="K19" s="64">
         <f>SUM($B$17:K17)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="65">
+      <c r="L19" s="64">
         <f>SUM($B$17:L17)</f>
         <v>0</v>
       </c>
-      <c r="M19" s="65">
+      <c r="M19" s="64">
         <f>SUM($B$17:M17)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="63">
+      <c r="N19" s="62">
         <f>M19</f>
         <v>0</v>
       </c>
-      <c r="O19" s="52"/>
+      <c r="O19" s="51"/>
     </row>
     <row r="20" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="40">
+      <c r="A20" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="39">
         <f>SUM($B$18:B18)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="39">
         <f>SUM($B$18:C18)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="39">
         <f>SUM($B$18:D18)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="39">
         <f>SUM($B$18:E18)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="39">
         <f>SUM($B$18:F18)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="39">
         <f>SUM($B$18:G18)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="39">
         <f>SUM($B$18:H18)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="40">
+      <c r="I20" s="39">
         <f>SUM($B$18:I18)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="39">
         <f>SUM($B$18:J18)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="40">
+      <c r="K20" s="39">
         <f>SUM($B$18:K18)</f>
         <v>0</v>
       </c>
-      <c r="L20" s="40">
+      <c r="L20" s="39">
         <f>SUM($B$18:L18)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="40">
+      <c r="M20" s="39">
         <f>SUM($B$18:M18)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="54">
+      <c r="N20" s="53">
         <f>M20</f>
         <v>0</v>
       </c>
-      <c r="O20" s="57">
+      <c r="O20" s="56">
         <f>IFERROR(N20/(B5+C5),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="75" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" s="77">
+      <c r="A21" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="76">
         <f t="shared" ref="B21:M21" si="3">IFERROR(B11/B18,0)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="77">
+      <c r="C21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D21" s="77">
+      <c r="D21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E21" s="77">
+      <c r="E21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F21" s="77">
+      <c r="F21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G21" s="77">
+      <c r="G21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H21" s="77">
+      <c r="H21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I21" s="77">
+      <c r="I21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="77">
+      <c r="J21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="77">
+      <c r="K21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="77">
+      <c r="L21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="77">
+      <c r="M21" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N21" s="76"/>
-      <c r="O21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="73"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="61">
+      <c r="A22" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="60">
         <f>IFERROR(B20/($B$5+$C$5),0)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="61">
+      <c r="C22" s="60">
         <f t="shared" ref="C22:M22" si="4">IFERROR(C20/($B$5+$C$5),0)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="61">
+      <c r="D22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H22" s="61">
+      <c r="H22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I22" s="61">
+      <c r="I22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="61">
+      <c r="J22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="61">
+      <c r="K22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L22" s="61">
+      <c r="L22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="61">
+      <c r="M22" s="60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N22" s="48"/>
+      <c r="N22" s="47"/>
     </row>
     <row r="23" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="51">
+      <c r="A23" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="50">
         <f>SUM($B11:B11)/$N$5</f>
         <v>7.9051383399209488E-2</v>
       </c>
-      <c r="C23" s="51">
+      <c r="C23" s="50">
         <f>SUM($B11:C11)/$N$11</f>
         <v>0.15810276679841898</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="50">
         <f>SUM($B11:D11)/$N$11</f>
         <v>0.24505928853754941</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="50">
         <f>SUM($B11:E11)/$N$11</f>
         <v>0.32411067193675891</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="50">
         <f>SUM($B11:F11)/$N$11</f>
         <v>0.39525691699604742</v>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="50">
         <f>SUM($B11:G11)/$N$11</f>
         <v>0.48221343873517786</v>
       </c>
-      <c r="H23" s="51">
+      <c r="H23" s="50">
         <f>SUM($B11:H11)/$N$11</f>
         <v>0.5731225296442688</v>
       </c>
-      <c r="I23" s="51">
+      <c r="I23" s="50">
         <f>SUM($B11:I11)/$N$11</f>
         <v>0.65612648221343872</v>
       </c>
-      <c r="J23" s="51">
+      <c r="J23" s="50">
         <f>SUM($B11:J11)/$N$11</f>
         <v>0.74308300395256921</v>
       </c>
-      <c r="K23" s="51">
+      <c r="K23" s="50">
         <f>SUM($B11:K11)/$N$11</f>
         <v>0.83003952569169959</v>
       </c>
-      <c r="L23" s="51">
+      <c r="L23" s="50">
         <f>SUM($B11:L11)/$N$11</f>
         <v>0.91304347826086951</v>
       </c>
-      <c r="M23" s="51">
+      <c r="M23" s="50">
         <f>SUM($B11:M11)/$N$11</f>
         <v>1</v>
       </c>
-      <c r="N23" s="41"/>
+      <c r="N23" s="40"/>
     </row>
     <row r="24" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="124" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" s="125"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="125"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="55" t="s">
-        <v>81</v>
+      <c r="A24" s="128" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="129"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="129"/>
+      <c r="M24" s="129"/>
+      <c r="N24" s="130"/>
+      <c r="O24" s="54" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="47">
+      <c r="A25" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="46">
         <f>B11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="46">
         <f>C11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="46">
         <f>D11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="46">
         <f>E11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="47">
+      <c r="F25" s="46">
         <f>F11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="46">
         <f>G11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="47">
+      <c r="H25" s="46">
         <f>H11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="47">
+      <c r="I25" s="46">
         <f>I11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="47">
+      <c r="J25" s="46">
         <f>J11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="47">
+      <c r="K25" s="46">
         <f>K11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="47">
+      <c r="L25" s="46">
         <f>L11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="M25" s="47">
+      <c r="M25" s="46">
         <f>M11*('Work Sheet'!$H$2/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="53">
+      <c r="N25" s="52">
         <f>SUM(B25:M25)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="58"/>
+      <c r="O25" s="57"/>
     </row>
     <row r="26" spans="1:17" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="60" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="49">
+      <c r="A26" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="48">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,1,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,2,1))</f>
         <v>0</v>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="48">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,2,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,3,1))</f>
         <v>0</v>
       </c>
-      <c r="D26" s="49">
+      <c r="D26" s="48">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,3,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,4,1))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,4,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,5,1))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,5,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,6,1))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,6,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,7,1))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,7,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,8,1))</f>
         <v>0</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,8,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,9,1))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,9,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,10,1))</f>
         <v>0</v>
       </c>
-      <c r="K26" s="40">
+      <c r="K26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,10,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,11,1))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="40">
+      <c r="L26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,11,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2,12,1))</f>
         <v>0</v>
       </c>
-      <c r="M26" s="40">
+      <c r="M26" s="39">
         <f>COUNTIFS('Work Sheet'!$B$17:$B$771,"Examen",'Work Sheet'!$C$17:$C$771,"1st Communication",'Work Sheet'!$A$17:$A$771,"&gt;="&amp;DATE('Work Sheet'!$B$2,12,1),'Work Sheet'!$A$17:$A$771,"&lt;"&amp;DATE('Work Sheet'!$B$2+1,1,1))</f>
         <v>0</v>
       </c>
-      <c r="N26" s="54">
+      <c r="N26" s="53">
         <f>SUM(B26:M26)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="62">
+      <c r="O26" s="61">
         <f>IFERROR(N26/D5,0)</f>
         <v>0</v>
       </c>
@@ -20181,362 +20185,362 @@
     </row>
     <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B30" s="116" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="117"/>
+      <c r="B30" s="120" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="121"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="118" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="119"/>
+      <c r="B31" s="122" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="123"/>
     </row>
     <row r="38" spans="21:21" x14ac:dyDescent="0.2">
       <c r="U38" s="7"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="115" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" s="115"/>
-      <c r="C65" s="115"/>
-      <c r="D65" s="115"/>
-      <c r="E65" s="115"/>
-      <c r="F65" s="115"/>
-      <c r="G65" s="115"/>
-      <c r="H65" s="115"/>
-      <c r="I65" s="115"/>
-      <c r="J65" s="115"/>
-      <c r="K65" s="115"/>
-      <c r="L65" s="115"/>
-      <c r="M65" s="115"/>
-      <c r="N65" s="115"/>
+      <c r="A65" s="119" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" s="119"/>
+      <c r="C65" s="119"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="119"/>
+      <c r="H65" s="119"/>
+      <c r="I65" s="119"/>
+      <c r="J65" s="119"/>
+      <c r="K65" s="119"/>
+      <c r="L65" s="119"/>
+      <c r="M65" s="119"/>
+      <c r="N65" s="119"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="B66" s="73">
+      <c r="A66" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="72">
         <f t="shared" ref="B66:M66" si="5">IF($B$31="Previsional (recommended)",B17,IF($B$31="Previsional Corrected",B68,B69))</f>
         <v>0</v>
       </c>
-      <c r="C66" s="73">
+      <c r="C66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D66" s="73">
+      <c r="D66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E66" s="73">
+      <c r="E66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F66" s="73">
+      <c r="F66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G66" s="73">
+      <c r="G66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H66" s="73">
+      <c r="H66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I66" s="73">
+      <c r="I66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J66" s="73">
+      <c r="J66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K66" s="73">
+      <c r="K66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L66" s="73">
+      <c r="L66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M66" s="73">
+      <c r="M66" s="72">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="78" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="73" cm="1">
+      <c r="A67" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" s="72" cm="1">
         <f t="array" aca="1" ref="B67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,1),_xlpm.this_floor,INDEX(_xlpm.floors,1),_xlpm.this_frac,INDEX(_xlpm.fracs,1),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(1&lt;=_xlpm.cur,B11,MAX(0,B11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>20</v>
       </c>
-      <c r="C67" s="73" cm="1">
+      <c r="C67" s="72" cm="1">
         <f t="array" aca="1" ref="C67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,2),_xlpm.this_floor,INDEX(_xlpm.floors,2),_xlpm.this_frac,INDEX(_xlpm.fracs,2),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(2&lt;=_xlpm.cur,C11,MAX(0,C11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>20</v>
       </c>
-      <c r="D67" s="73" cm="1">
+      <c r="D67" s="72" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,3),_xlpm.this_floor,INDEX(_xlpm.floors,3),_xlpm.this_frac,INDEX(_xlpm.fracs,3),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(3&lt;=_xlpm.cur,D11,MAX(0,D11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>22</v>
       </c>
-      <c r="E67" s="73" cm="1">
+      <c r="E67" s="72" cm="1">
         <f t="array" aca="1" ref="E67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,4),_xlpm.this_floor,INDEX(_xlpm.floors,4),_xlpm.this_frac,INDEX(_xlpm.fracs,4),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(4&lt;=_xlpm.cur,E11,MAX(0,E11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>20</v>
       </c>
-      <c r="F67" s="73" cm="1">
+      <c r="F67" s="72" cm="1">
         <f t="array" aca="1" ref="F67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,5),_xlpm.this_floor,INDEX(_xlpm.floors,5),_xlpm.this_frac,INDEX(_xlpm.fracs,5),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(5&lt;=_xlpm.cur,F11,MAX(0,F11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>18</v>
       </c>
-      <c r="G67" s="73" cm="1">
+      <c r="G67" s="72" cm="1">
         <f t="array" aca="1" ref="G67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,6),_xlpm.this_floor,INDEX(_xlpm.floors,6),_xlpm.this_frac,INDEX(_xlpm.fracs,6),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(6&lt;=_xlpm.cur,G11,MAX(0,G11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>22</v>
       </c>
-      <c r="H67" s="73" cm="1">
+      <c r="H67" s="72" cm="1">
         <f t="array" aca="1" ref="H67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,7),_xlpm.this_floor,INDEX(_xlpm.floors,7),_xlpm.this_frac,INDEX(_xlpm.fracs,7),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(7&lt;=_xlpm.cur,H11,MAX(0,H11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>23</v>
       </c>
-      <c r="I67" s="73" cm="1">
+      <c r="I67" s="72" cm="1">
         <f t="array" aca="1" ref="I67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,8),_xlpm.this_floor,INDEX(_xlpm.floors,8),_xlpm.this_frac,INDEX(_xlpm.fracs,8),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(8&lt;=_xlpm.cur,I11,MAX(0,I11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>21</v>
       </c>
-      <c r="J67" s="73" cm="1">
+      <c r="J67" s="72" cm="1">
         <f t="array" aca="1" ref="J67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,9),_xlpm.this_floor,INDEX(_xlpm.floors,9),_xlpm.this_frac,INDEX(_xlpm.fracs,9),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(9&lt;=_xlpm.cur,J11,MAX(0,J11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>22</v>
       </c>
-      <c r="K67" s="73" cm="1">
+      <c r="K67" s="72" cm="1">
         <f t="array" aca="1" ref="K67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,10),_xlpm.this_floor,INDEX(_xlpm.floors,10),_xlpm.this_frac,INDEX(_xlpm.fracs,10),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(10&lt;=_xlpm.cur,K11,MAX(0,K11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>22</v>
       </c>
-      <c r="L67" s="73" cm="1">
+      <c r="L67" s="72" cm="1">
         <f t="array" aca="1" ref="L67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,11),_xlpm.this_floor,INDEX(_xlpm.floors,11),_xlpm.this_frac,INDEX(_xlpm.fracs,11),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(11&lt;=_xlpm.cur,L11,MAX(0,L11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>21</v>
       </c>
-      <c r="M67" s="73" cm="1">
+      <c r="M67" s="72" cm="1">
         <f t="array" aca="1" ref="M67" ca="1">_xlfn.LET(_xlpm.cur,MONTH(TODAY()),_xlpm.missing,MAX(0,$L$5-$N$10),_xlpm.fut,B11:M11*(COLUMN(B11:M11)-COLUMN(B11)+1&gt;_xlpm.cur),_xlpm.fut_tot,SUM(_xlpm.fut),_xlpm.shares,IF(_xlpm.fut_tot&gt;0,_xlpm.missing*_xlpm.fut/_xlpm.fut_tot,0),_xlpm.floors,INT(_xlpm.shares),_xlpm.leftover,_xlpm.missing-SUM(_xlpm.floors),_xlpm.fracs,_xlpm.shares-_xlpm.floors,_xlpm.this_share,INDEX(_xlpm.shares,12),_xlpm.this_floor,INDEX(_xlpm.floors,12),_xlpm.this_frac,INDEX(_xlpm.fracs,12),_xlpm.extra,IF(_xlpm.leftover&gt;0,IF(_xlpm.this_frac&gt;=LARGE(_xlpm.fracs,_xlpm.leftover),1,0),0),IF(12&lt;=_xlpm.cur,M11,MAX(0,M11-(_xlpm.this_floor+_xlpm.extra))))</f>
         <v>22</v>
       </c>
-      <c r="N67" s="73">
+      <c r="N67" s="72">
         <f ca="1">SUM(B67:M67)</f>
         <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="78" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="73">
+      <c r="A68" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B68" s="72">
         <f ca="1">B67*($E$5/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="C68" s="73">
+      <c r="C68" s="72">
         <f t="shared" ref="C68:N68" ca="1" si="6">C67*($E$5/$N$5)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="73">
+      <c r="D68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="E68" s="73">
+      <c r="E68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="F68" s="73">
+      <c r="F68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="G68" s="73">
+      <c r="G68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="H68" s="73">
+      <c r="H68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="I68" s="73">
+      <c r="I68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="J68" s="73">
+      <c r="J68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="K68" s="73">
+      <c r="K68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="L68" s="73">
+      <c r="L68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M68" s="73">
+      <c r="M68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="N68" s="73">
+      <c r="N68" s="72">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="78" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="73">
+      <c r="A69" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B69" s="72">
         <f>$E$5/12</f>
         <v>0</v>
       </c>
-      <c r="C69" s="73">
+      <c r="C69" s="72">
         <f t="shared" ref="C69:M69" si="7">$E$5/12</f>
         <v>0</v>
       </c>
-      <c r="D69" s="73">
+      <c r="D69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E69" s="73">
+      <c r="E69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F69" s="73">
+      <c r="F69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G69" s="73">
+      <c r="G69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H69" s="73">
+      <c r="H69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I69" s="73">
+      <c r="I69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J69" s="73">
+      <c r="J69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K69" s="73">
+      <c r="K69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L69" s="73">
+      <c r="L69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M69" s="73">
+      <c r="M69" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N69" s="73"/>
+      <c r="N69" s="72"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" s="73">
+      <c r="A70" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="72">
         <f ca="1">SUM($B$68:B68)</f>
         <v>0</v>
       </c>
-      <c r="C70" s="73">
+      <c r="C70" s="72">
         <f ca="1">SUM($B$68:C68)</f>
         <v>0</v>
       </c>
-      <c r="D70" s="73">
+      <c r="D70" s="72">
         <f ca="1">SUM($B$68:D68)</f>
         <v>0</v>
       </c>
-      <c r="E70" s="73">
+      <c r="E70" s="72">
         <f ca="1">SUM($B$68:E68)</f>
         <v>0</v>
       </c>
-      <c r="F70" s="73">
+      <c r="F70" s="72">
         <f ca="1">SUM($B$68:F68)</f>
         <v>0</v>
       </c>
-      <c r="G70" s="73">
+      <c r="G70" s="72">
         <f ca="1">SUM($B$68:G68)</f>
         <v>0</v>
       </c>
-      <c r="H70" s="73">
+      <c r="H70" s="72">
         <f ca="1">SUM($B$68:H68)</f>
         <v>0</v>
       </c>
-      <c r="I70" s="73">
+      <c r="I70" s="72">
         <f ca="1">SUM($B$68:I68)</f>
         <v>0</v>
       </c>
-      <c r="J70" s="73">
+      <c r="J70" s="72">
         <f ca="1">SUM($B$68:J68)</f>
         <v>0</v>
       </c>
-      <c r="K70" s="73">
+      <c r="K70" s="72">
         <f ca="1">SUM($B$68:K68)</f>
         <v>0</v>
       </c>
-      <c r="L70" s="73">
+      <c r="L70" s="72">
         <f ca="1">SUM($B$68:L68)</f>
         <v>0</v>
       </c>
-      <c r="M70" s="73">
+      <c r="M70" s="72">
         <f ca="1">SUM($B$68:M68)</f>
         <v>0</v>
       </c>
-      <c r="N70" s="73"/>
+      <c r="N70" s="72"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="B71" s="73">
+      <c r="A71" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="72">
         <f>IF($B$31="Previsional (recommended)",B19,IF($B$31="Previsional Corrected",B70,$E$5/12*1))</f>
         <v>0</v>
       </c>
-      <c r="C71" s="73">
+      <c r="C71" s="72">
         <f>IF($B$31="Previsional (recommended)",C19,IF($B$31="Previsional Corrected",C70,$E$5/12*2))</f>
         <v>0</v>
       </c>
-      <c r="D71" s="73">
+      <c r="D71" s="72">
         <f>IF($B$31="Previsional (recommended)",D19,IF($B$31="Previsional Corrected",D70,$E$5/12*3))</f>
         <v>0</v>
       </c>
-      <c r="E71" s="73">
+      <c r="E71" s="72">
         <f>IF($B$31="Previsional (recommended)",E19,IF($B$31="Previsional Corrected",E70,$E$5/12*4))</f>
         <v>0</v>
       </c>
-      <c r="F71" s="73">
+      <c r="F71" s="72">
         <f>IF($B$31="Previsional (recommended)",F19,IF($B$31="Previsional Corrected",F70,$E$5/12*5))</f>
         <v>0</v>
       </c>
-      <c r="G71" s="73">
+      <c r="G71" s="72">
         <f>IF($B$31="Previsional (recommended)",G19,IF($B$31="Previsional Corrected",G70,$E$5/12*6))</f>
         <v>0</v>
       </c>
-      <c r="H71" s="73">
+      <c r="H71" s="72">
         <f>IF($B$31="Previsional (recommended)",H19,IF($B$31="Previsional Corrected",H70,$E$5/12*7))</f>
         <v>0</v>
       </c>
-      <c r="I71" s="73">
+      <c r="I71" s="72">
         <f>IF($B$31="Previsional (recommended)",I19,IF($B$31="Previsional Corrected",I70,$E$5/12*8))</f>
         <v>0</v>
       </c>
-      <c r="J71" s="73">
+      <c r="J71" s="72">
         <f>IF($B$31="Previsional (recommended)",J19,IF($B$31="Previsional Corrected",J70,$E$5/12*9))</f>
         <v>0</v>
       </c>
-      <c r="K71" s="73">
+      <c r="K71" s="72">
         <f>IF($B$31="Previsional (recommended)",K19,IF($B$31="Previsional Corrected",K70,$E$5/12*10))</f>
         <v>0</v>
       </c>
-      <c r="L71" s="73">
+      <c r="L71" s="72">
         <f>IF($B$31="Previsional (recommended)",L19,IF($B$31="Previsional Corrected",L70,$E$5/12*11))</f>
         <v>0</v>
       </c>
-      <c r="M71" s="73">
+      <c r="M71" s="72">
         <f>IF($B$31="Previsional (recommended)",M19,IF($B$31="Previsional Corrected",M70,$E$5/12*12))</f>
         <v>0</v>
       </c>
@@ -20619,17 +20623,17 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -20651,121 +20655,121 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="99" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+    </row>
+    <row r="5" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="88" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="102" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+    </row>
+    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+    </row>
+    <row r="7" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="88" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="100" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+    </row>
+    <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="89" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="101" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+    </row>
+    <row r="9" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+    </row>
+    <row r="11" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="86" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="138" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+    </row>
+    <row r="12" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="92" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="92" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-    </row>
-    <row r="5" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="141" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="141"/>
-      <c r="E5" s="141"/>
-    </row>
-    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="90" t="s">
+    </row>
+    <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="142" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="142"/>
-      <c r="E6" s="142"/>
-    </row>
-    <row r="7" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="89" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="139" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-    </row>
-    <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="90" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="140" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
-    </row>
-    <row r="9" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="89" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="139" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-    </row>
-    <row r="11" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="87" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-    </row>
-    <row r="12" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="93" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="93" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="98" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="98" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="94" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="95" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="14" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="92"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="91"/>
     </row>
     <row r="15" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="91"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="90"/>
     </row>
     <row r="16" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="92"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -24441,28 +24445,28 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -24472,17 +24476,17 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -24497,6 +24501,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD56ED26D91545469ECED54A4FE3D042" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9df94f712de2706e123dde0e08998a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41e9aca9-e27a-4d68-85e7-df7514394499" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e43637212972ea02e5fd49153bea6e3" ns3:_="">
     <xsd:import namespace="41e9aca9-e27a-4d68-85e7-df7514394499"/>
@@ -24628,15 +24641,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60E1B745-867C-423C-9F93-50CAD41A1ED0}">
   <ds:schemaRefs>
@@ -24654,6 +24658,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4AB0541-0BDB-4B2A-92CE-F116BE04472D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE34781-ED31-4C5F-91DA-BA4537EE8E83}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24669,12 +24681,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4AB0541-0BDB-4B2A-92CE-F116BE04472D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>